--- a/docs/characters/data/RefactorTactics_Characters_Wiki_Data_v0.4.xlsx
+++ b/docs/characters/data/RefactorTactics_Characters_Wiki_Data_v0.4.xlsx
@@ -7748,7 +7748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="52" min="1" max="1"/>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-FAST</t>
+          <t>RT-FEAT-REACTION-CLASH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-FAST-ACTION</t>
+          <t>RT-FEAT-REACTION-FAST</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OPPORTUNITY</t>
+          <t>RT-FEAT-REACTION-FAST-ACTION</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OVERWATCH</t>
+          <t>RT-FEAT-REACTION-OPPORTUNITY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-REACTION-OVERWATCH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8610,12 +8610,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Guide.RegoleFondamentali</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-DETERMINISM</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8625,19 +8625,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>docs/wiki/game/regole-fondamentali.md</t>
+          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Guide.RegoleFondamentali</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-TURNLOG</t>
+          <t>RT-FEAT-REACTION-PROFILE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8647,19 +8647,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>docs/wiki/game/regole-fondamentali.md</t>
+          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guide.SinergieECombinazioni</t>
+          <t>Guide.RegoleFondamentali</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-CORE-DETERMINISM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8669,19 +8669,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>docs/wiki/game/sinergie-e-combinazioni.md</t>
+          <t>docs/wiki/game/regole-fondamentali.md</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guide.StrutturaDelRound</t>
+          <t>Guide.RegoleFondamentali</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-TURN</t>
+          <t>RT-FEAT-CORE-TURNLOG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8691,19 +8691,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>docs/wiki/game/struttura-del-round.md</t>
+          <t>docs/wiki/game/regole-fondamentali.md</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.SinergieECombinazioni</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-MEMORY</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8713,19 +8713,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>docs/wiki/game/sinergie-e-combinazioni.md</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.StrutturaDelRound</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-NOISE</t>
+          <t>RT-FEAT-CORE-TURN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>docs/wiki/game/struttura-del-round.md</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-TEAM-KNOWLEDGE</t>
+          <t>RT-FEAT-PERCEPTION-MEMORY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-VISION</t>
+          <t>RT-FEAT-PERCEPTION-NOISE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8786,66 +8786,66 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hero.Aurora</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-PERCEPTION-TEAM-KNOWLEDGE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/aurora.md</t>
+          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hero.Bastion</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-PERCEPTION-VISION</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/bastion.md</t>
+          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hero.Bastion</t>
+          <t>Hero.Aurora</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/bastion.md</t>
+          <t>docs/characters/v0.2/aurora.md</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8874,34 +8874,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hero.Flux</t>
+          <t>Hero.Bastion</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/flux.md</t>
+          <t>docs/characters/v0.1/bastion.md</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hero.Flux</t>
+          <t>Hero.Bastion</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-ELECTRIC</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/flux.md</t>
+          <t>docs/characters/v0.1/bastion.md</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8940,56 +8940,56 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hero.Kwang</t>
+          <t>Hero.Flux</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-ENV-ELECTRIC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/kwang.md</t>
+          <t>docs/characters/v0.1/flux.md</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hero.Murdock</t>
+          <t>Hero.Flux</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/murdock.md</t>
+          <t>docs/characters/v0.1/flux.md</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hero.Riva</t>
+          <t>Hero.Kwang</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8999,29 +8999,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/riva.md</t>
+          <t>docs/characters/v0.2/kwang.md</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hero.Riva</t>
+          <t>Hero.Murdock</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/riva.md</t>
+          <t>docs/characters/v0.2/murdock.md</t>
         </is>
       </c>
     </row>
@@ -9033,12 +9033,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-WATER</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9050,34 +9050,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hero.Steel</t>
+          <t>Hero.Riva</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/steel.md</t>
+          <t>docs/characters/v0.1/riva.md</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hero.Vektor</t>
+          <t>Hero.Riva</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-PREDICTIVE</t>
+          <t>RT-FEAT-ENV-WATER</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9087,19 +9087,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/vektor.md</t>
+          <t>docs/characters/v0.1/riva.md</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hero.Vektor</t>
+          <t>Hero.Steel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/vektor.md</t>
+          <t>docs/characters/v0.2/steel.md</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-ACTION-PREDICTIVE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9138,56 +9138,56 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mechanic.AcquaEElettricita</t>
+          <t>Hero.Vektor</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-ELECTRIC</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
+          <t>docs/characters/v0.1/vektor.md</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mechanic.AcquaEElettricita</t>
+          <t>Hero.Vektor</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-WATER</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
+          <t>docs/characters/v0.1/vektor.md</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mechanic.Collisioni</t>
+          <t>Mechanic.AcquaEElettricita</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
+          <t>RT-FEAT-ENV-ELECTRIC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9197,19 +9197,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/collisioni.md</t>
+          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mechanic.Collisioni</t>
+          <t>Mechanic.AcquaEElettricita</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-ENGINE</t>
+          <t>RT-FEAT-ENV-WATER</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9219,19 +9219,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/collisioni.md</t>
+          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mechanic.Coperture</t>
+          <t>Mechanic.Collisioni</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-COVER</t>
+          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9241,19 +9241,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/coperture.md</t>
+          <t>docs/wiki/meccaniche/collisioni.md</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mechanic.Coperture</t>
+          <t>Mechanic.Collisioni</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
+          <t>RT-FEAT-ACTION-ENGINE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9263,19 +9263,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/coperture.md</t>
+          <t>docs/wiki/meccaniche/collisioni.md</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mechanic.FacingEDirezionalita</t>
+          <t>Mechanic.Coperture</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-FACING</t>
+          <t>RT-FEAT-MAP-COVER</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9285,19 +9285,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/facing-e-direzionalita.md</t>
+          <t>docs/wiki/meccaniche/coperture.md</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mechanic.FuocoEStati</t>
+          <t>Mechanic.Coperture</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-FIRE</t>
+          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -9307,19 +9307,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
+          <t>docs/wiki/meccaniche/coperture.md</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mechanic.FuocoEStati</t>
+          <t>Mechanic.FacingEDirezionalita</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-STATUS</t>
+          <t>RT-FEAT-MAP-FACING</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9329,19 +9329,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
+          <t>docs/wiki/meccaniche/facing-e-direzionalita.md</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mechanic.ObiettiviDinamici</t>
+          <t>Mechanic.FuocoEStati</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
+          <t>RT-FEAT-ENV-FIRE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9351,19 +9351,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/obiettivi-dinamici.md</t>
+          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mechanic.Overwatch</t>
+          <t>Mechanic.FuocoEStati</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OVERWATCH</t>
+          <t>RT-FEAT-ENV-STATUS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9373,19 +9373,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/overwatch.md</t>
+          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mechanic.Ponti</t>
+          <t>Mechanic.ObiettiviDinamici</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9395,19 +9395,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/ponti.md</t>
+          <t>docs/wiki/meccaniche/obiettivi-dinamici.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mechanic.Porte</t>
+          <t>Mechanic.Overwatch</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+          <t>RT-FEAT-REACTION-OVERWATCH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9417,19 +9417,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/porte.md</t>
+          <t>docs/wiki/meccaniche/overwatch.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mechanic.TopologiaDinamica</t>
+          <t>Mechanic.Ponti</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9439,19 +9439,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
+          <t>docs/wiki/meccaniche/ponti.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mechanic.TopologiaDinamica</t>
+          <t>Mechanic.Porte</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9461,58 +9461,58 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
+          <t>docs/wiki/meccaniche/porte.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Scenario.Team.Conflux.FluxRiva.ConductiveFlood</t>
+          <t>Mechanic.TopologiaDinamica</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RT-FEAT-FACTION-SCENARIOS</t>
+          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>validates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>pianificato</t>
+          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Scenario.Team.Constrine.BastionVektor.OnlyExit</t>
+          <t>Mechanic.TopologiaDinamica</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RT-FEAT-FACTION-SCENARIOS</t>
+          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>validates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>pianificato</t>
+          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Scenario.Team.Resonance.AuroraKwang.FrozenAnchor</t>
+          <t>Scenario.Team.Conflux.FluxRiva.ConductiveFlood</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9534,20 +9534,64 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>Scenario.Team.Constrine.BastionVektor.OnlyExit</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RT-FEAT-FACTION-SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>validates</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>pianificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Scenario.Team.Resonance.AuroraKwang.FrozenAnchor</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>RT-FEAT-FACTION-SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>validates</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>pianificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Scenario.Team.Sentinel.SteelMurdock.HoldTheLine</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>RT-FEAT-FACTION-SCENARIOS</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>validates</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>pianificato</t>
         </is>

--- a/docs/characters/data/RefactorTactics_Characters_Wiki_Data_v0.4.xlsx
+++ b/docs/characters/data/RefactorTactics_Characters_Wiki_Data_v0.4.xlsx
@@ -7748,7 +7748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="52" min="1" max="1"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>docs/wiki/fazioni/conflux.md</t>
+          <t>wiki:conflux</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>docs/wiki/fazioni/constrine.md</t>
+          <t>wiki:constrine</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>docs/wiki/fazioni/resonance.md</t>
+          <t>wiki:resonance</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>docs/wiki/fazioni/sentinel-directorate.md</t>
+          <t>wiki:sentinel-directorate</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>docs/wiki/game/avversario-bot.md</t>
+          <t>wiki:avversario-bot</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RT-FEAT-BOT-TACTICAL</t>
+          <t>RT-FEAT-BOT-BELIEF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7921,19 +7921,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>docs/wiki/game/avversario-bot.md</t>
+          <t>wiki:avversario-bot</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Guide.AzioniEMovimento</t>
+          <t>Guide.AvversarioBot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-COOLDOWNS</t>
+          <t>RT-FEAT-BOT-FAIRNESS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7943,19 +7943,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:avversario-bot</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guide.AzioniEMovimento</t>
+          <t>Guide.AvversarioBot</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
+          <t>RT-FEAT-BOT-PREDICTIVE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7965,19 +7965,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:avversario-bot</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Guide.AzioniEMovimento</t>
+          <t>Guide.AvversarioBot</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-ENGINE</t>
+          <t>RT-FEAT-BOT-TACTICAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:avversario-bot</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-GENERIC</t>
+          <t>RT-FEAT-ACTION-BASIC-ATTACK-PROFILES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-MOVE-PROFILES</t>
+          <t>RT-FEAT-ACTION-BUDGET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-SUPERS</t>
+          <t>RT-FEAT-ACTION-COOLDOWNS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-PATHFINDING</t>
+          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8075,19 +8075,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>docs/wiki/game/azioni-e-movimento.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Guide.CombattimentoETargeting</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-LOS</t>
+          <t>RT-FEAT-ACTION-ENGINE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8097,19 +8097,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>docs/wiki/game/combattimento-e-targeting.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Guide.CombattimentoETargeting</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-WARNINGS</t>
+          <t>RT-FEAT-ACTION-GENERIC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8119,19 +8119,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>docs/wiki/game/combattimento-e-targeting.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guide.ComeSiGioca</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RT-FEAT-NET-PRIVATE-PLANNING</t>
+          <t>RT-FEAT-ACTION-MOVE-PROFILES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8141,19 +8141,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>docs/wiki/game/come-si-gioca.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guide.ComeSiGioca</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-ACTION-GHOSTS</t>
+          <t>RT-FEAT-ACTION-MOVEMENT-COMPAT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8163,19 +8163,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>docs/wiki/game/come-si-gioca.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Guide.ComeSiGioca</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-CERTAINTY</t>
+          <t>RT-FEAT-ACTION-SUPERS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8185,19 +8185,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>docs/wiki/game/come-si-gioca.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Guide.ComeSiGioca</t>
+          <t>Guide.AzioniEMovimento</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-PLANNING</t>
+          <t>RT-FEAT-MAP-PATHFINDING</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8207,19 +8207,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>docs/wiki/game/come-si-gioca.md</t>
+          <t>wiki:azioni-e-movimento</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Guide.ComeSiGioca</t>
+          <t>Guide.CombattimentoETargeting</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-TACTICAL-CAMERA</t>
+          <t>RT-FEAT-MAP-LOS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8229,19 +8229,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>docs/wiki/game/come-si-gioca.md</t>
+          <t>wiki:combattimento-e-targeting</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Guide.EsempioDiRound</t>
+          <t>Guide.CombattimentoETargeting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-PLAYBACK</t>
+          <t>RT-FEAT-UI-WARNINGS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8251,19 +8251,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>docs/wiki/game/esempio-di-round.md</t>
+          <t>wiki:combattimento-e-targeting</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Guide.EsempioDiRound</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-TURN</t>
+          <t>RT-FEAT-NET-PRIVATE-PLANNING</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8273,19 +8273,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>docs/wiki/game/esempio-di-round.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Guide.EsempioDiRound</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RT-FEAT-UI-COMBAT-LOG</t>
+          <t>RT-FEAT-UI-ACTION-GHOSTS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8295,19 +8295,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>docs/wiki/game/esempio-di-round.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Guide.MappaTerreniEAmbiente</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-ICE</t>
+          <t>RT-FEAT-UI-CERTAINTY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>docs/wiki/game/mappa-terreni-e-ambiente.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Guide.MappaTerreniEAmbiente</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-STEAM</t>
+          <t>RT-FEAT-UI-PLANNING</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8339,19 +8339,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>docs/wiki/game/mappa-terreni-e-ambiente.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Guide.MappaTerreniEAmbiente</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-TERRAIN</t>
+          <t>RT-FEAT-UI-SCREEN-HUD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8361,19 +8361,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>docs/wiki/game/mappa-terreni-e-ambiente.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Guide.MappaTerreniEAmbiente</t>
+          <t>Guide.ComeSiGioca</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-HEXGRAPH</t>
+          <t>RT-FEAT-UI-TACTICAL-CAMERA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8383,19 +8383,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>docs/wiki/game/mappa-terreni-e-ambiente.md</t>
+          <t>wiki:come-si-gioca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Guide.MappaTerreniEAmbiente</t>
+          <t>Guide.EsempioDiRound</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-HIGH-GROUND</t>
+          <t>RT-FEAT-CORE-PLAYBACK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8405,19 +8405,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>docs/wiki/game/mappa-terreni-e-ambiente.md</t>
+          <t>wiki:esempio-di-round</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Guide.ObiettiviEFinePartita</t>
+          <t>Guide.EsempioDiRound</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RT-FEAT-MATCH-END-CONDITIONS</t>
+          <t>RT-FEAT-CORE-TURN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8427,19 +8427,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>docs/wiki/game/obiettivi-e-fine-partita.md</t>
+          <t>wiki:esempio-di-round</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Guide.ObiettiviEFinePartita</t>
+          <t>Guide.EsempioDiRound</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
+          <t>RT-FEAT-UI-COMBAT-LOG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8449,19 +8449,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>docs/wiki/game/obiettivi-e-fine-partita.md</t>
+          <t>wiki:esempio-di-round</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.MappaTerreniEAmbiente</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-PREDICTIVE</t>
+          <t>RT-FEAT-ENV-ICE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8471,19 +8471,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:mappa-terreni-e-ambiente</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.MappaTerreniEAmbiente</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-DECISION-BOUNDARY</t>
+          <t>RT-FEAT-ENV-STEAM</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8493,19 +8493,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:mappa-terreni-e-ambiente</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.MappaTerreniEAmbiente</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-CLASH</t>
+          <t>RT-FEAT-ENV-TERRAIN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8515,19 +8515,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:mappa-terreni-e-ambiente</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.MappaTerreniEAmbiente</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-FAST</t>
+          <t>RT-FEAT-MAP-HEXGRAPH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8537,19 +8537,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:mappa-terreni-e-ambiente</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.MappaTerreniEAmbiente</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-FAST-ACTION</t>
+          <t>RT-FEAT-MAP-HIGH-GROUND</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8559,19 +8559,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:mappa-terreni-e-ambiente</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.ObiettiviEFinePartita</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OPPORTUNITY</t>
+          <t>RT-FEAT-MATCH-END-CONDITIONS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8581,19 +8581,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:obiettivi-e-fine-partita</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.ObiettiviEFinePartita</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OVERWATCH</t>
+          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8603,19 +8603,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:obiettivi-e-fine-partita</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Guide.ReazioniOverwatchEPrevisioni</t>
+          <t>Guide.PlanningECoordinazione</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-ACTION-PLAN-VALIDATION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:planning-e-coordinazione</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PROFILE</t>
+          <t>RT-FEAT-ACTION-PREDICTIVE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8647,19 +8647,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>docs/wiki/game/reazioni-overwatch-e-previsioni.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guide.RegoleFondamentali</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-DETERMINISM</t>
+          <t>RT-FEAT-CORE-DECISION-BOUNDARY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8669,19 +8669,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>docs/wiki/game/regole-fondamentali.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guide.RegoleFondamentali</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-TURNLOG</t>
+          <t>RT-FEAT-CORE-DECISION-TIME-BANK</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8691,19 +8691,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>docs/wiki/game/regole-fondamentali.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Guide.SinergieECombinazioni</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-REACTION-CLASH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8713,19 +8713,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>docs/wiki/game/sinergie-e-combinazioni.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Guide.StrutturaDelRound</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RT-FEAT-CORE-TURN</t>
+          <t>RT-FEAT-REACTION-FAST</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8735,19 +8735,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>docs/wiki/game/struttura-del-round.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-MEMORY</t>
+          <t>RT-FEAT-REACTION-FAST-ACTION</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8757,19 +8757,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-NOISE</t>
+          <t>RT-FEAT-REACTION-OPPORTUNITY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8779,19 +8779,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-TEAM-KNOWLEDGE</t>
+          <t>RT-FEAT-REACTION-OVERWATCH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8801,19 +8801,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Guide.VisibilitaRumoreEInformazione</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RT-FEAT-PERCEPTION-VISION</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8823,217 +8823,217 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>docs/wiki/game/visibilita-rumore-e-informazione.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hero.Aurora</t>
+          <t>Guide.ReazioniOverwatchEPrevisioni</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-REACTION-PROFILE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/aurora.md</t>
+          <t>wiki:reazioni-overwatch-e-previsioni</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hero.Bastion</t>
+          <t>Guide.RegoleFondamentali</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-CORE-DETERMINISM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/bastion.md</t>
+          <t>wiki:regole-fondamentali</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hero.Bastion</t>
+          <t>Guide.RegoleFondamentali</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
+          <t>RT-FEAT-CORE-TURNLOG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/bastion.md</t>
+          <t>wiki:regole-fondamentali</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hero.Bastion</t>
+          <t>Guide.SinergieECombinazioni</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/bastion.md</t>
+          <t>wiki:sinergie-e-combinazioni</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hero.Flux</t>
+          <t>Guide.StrutturaDelRound</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-CORE-TURN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/flux.md</t>
+          <t>wiki:struttura-del-round</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hero.Flux</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-ELECTRIC</t>
+          <t>RT-FEAT-PERCEPTION-MEMORY</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/flux.md</t>
+          <t>wiki:visibilita-rumore-e-informazione</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hero.Flux</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-PERCEPTION-NOISE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/flux.md</t>
+          <t>wiki:visibilita-rumore-e-informazione</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hero.Kwang</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-PERCEPTION-TEAM-KNOWLEDGE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/kwang.md</t>
+          <t>wiki:visibilita-rumore-e-informazione</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hero.Murdock</t>
+          <t>Guide.VisibilitaRumoreEInformazione</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-PERCEPTION-VISION</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/murdock.md</t>
+          <t>wiki:visibilita-rumore-e-informazione</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hero.Riva</t>
+          <t>Hero.Aurora</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9043,41 +9043,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/riva.md</t>
+          <t>docs/characters/v0.2/aurora.md</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hero.Riva</t>
+          <t>Hero.Bastion</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/riva.md</t>
+          <t>docs/characters/v0.1/bastion.md</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hero.Riva</t>
+          <t>Hero.Bastion</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-WATER</t>
+          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9087,85 +9087,85 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/riva.md</t>
+          <t>docs/characters/v0.1/bastion.md</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hero.Steel</t>
+          <t>Hero.Bastion</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V02-ROSTER</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>docs/characters/v0.2/steel.md</t>
+          <t>docs/characters/v0.1/bastion.md</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hero.Vektor</t>
+          <t>Hero.Flux</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-PREDICTIVE</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>demonstrates</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/vektor.md</t>
+          <t>docs/characters/v0.1/flux.md</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hero.Vektor</t>
+          <t>Hero.Flux</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RT-FEAT-CHAR-V01-ROSTER</t>
+          <t>RT-FEAT-ENV-ELECTRIC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/vektor.md</t>
+          <t>docs/characters/v0.1/flux.md</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hero.Vektor</t>
+          <t>Hero.Flux</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-PREPARED</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9175,217 +9175,217 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>docs/characters/v0.1/vektor.md</t>
+          <t>docs/characters/v0.1/flux.md</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mechanic.AcquaEElettricita</t>
+          <t>Hero.Kwang</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-ELECTRIC</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
+          <t>docs/characters/v0.2/kwang.md</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mechanic.AcquaEElettricita</t>
+          <t>Hero.Murdock</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-WATER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/acqua-e-elettricita.md</t>
+          <t>docs/characters/v0.2/murdock.md</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mechanic.Collisioni</t>
+          <t>Hero.Riva</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/collisioni.md</t>
+          <t>docs/characters/v0.1/riva.md</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mechanic.Collisioni</t>
+          <t>Hero.Riva</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RT-FEAT-ACTION-ENGINE</t>
+          <t>RT-FEAT-ENV-SYSTEMIC-COMBOS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/collisioni.md</t>
+          <t>docs/characters/v0.1/riva.md</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mechanic.Coperture</t>
+          <t>Hero.Riva</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-COVER</t>
+          <t>RT-FEAT-ENV-WATER</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/coperture.md</t>
+          <t>docs/characters/v0.1/riva.md</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mechanic.Coperture</t>
+          <t>Hero.Steel</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
+          <t>RT-FEAT-CHAR-V02-ROSTER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/coperture.md</t>
+          <t>docs/characters/v0.2/steel.md</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mechanic.FacingEDirezionalita</t>
+          <t>Hero.Vektor</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-FACING</t>
+          <t>RT-FEAT-ACTION-PREDICTIVE</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/facing-e-direzionalita.md</t>
+          <t>docs/characters/v0.1/vektor.md</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mechanic.FuocoEStati</t>
+          <t>Hero.Vektor</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-FIRE</t>
+          <t>RT-FEAT-CHAR-V01-ROSTER</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>release</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
+          <t>docs/characters/v0.1/vektor.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mechanic.FuocoEStati</t>
+          <t>Hero.Vektor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RT-FEAT-ENV-STATUS</t>
+          <t>RT-FEAT-REACTION-PREPARED</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>documents</t>
+          <t>demonstrates</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/fuoco-e-stati.md</t>
+          <t>docs/characters/v0.1/vektor.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mechanic.ObiettiviDinamici</t>
+          <t>Mechanic.AcquaEElettricita</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
+          <t>RT-FEAT-ENV-ELECTRIC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9395,19 +9395,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/obiettivi-dinamici.md</t>
+          <t>wiki:acqua-e-elettricita</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mechanic.Overwatch</t>
+          <t>Mechanic.AcquaEElettricita</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RT-FEAT-REACTION-OVERWATCH</t>
+          <t>RT-FEAT-ENV-WATER</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9417,19 +9417,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/overwatch.md</t>
+          <t>wiki:acqua-e-elettricita</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mechanic.Ponti</t>
+          <t>Mechanic.Collisioni</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+          <t>RT-FEAT-ACTION-DASH-DISPLACEMENT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -9439,19 +9439,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/ponti.md</t>
+          <t>wiki:collisioni</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mechanic.Porte</t>
+          <t>Mechanic.Collisioni</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+          <t>RT-FEAT-ACTION-ENGINE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -9461,19 +9461,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/porte.md</t>
+          <t>wiki:collisioni</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mechanic.TopologiaDinamica</t>
+          <t>Mechanic.Coperture</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+          <t>RT-FEAT-MAP-COVER</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9483,19 +9483,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
+          <t>wiki:coperture</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mechanic.TopologiaDinamica</t>
+          <t>Mechanic.Coperture</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+          <t>RT-FEAT-MAP-DYNAMIC-COVER</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9505,93 +9505,335 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>docs/wiki/meccaniche/topologia-dinamica.md</t>
+          <t>wiki:coperture</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Scenario.Team.Conflux.FluxRiva.ConductiveFlood</t>
+          <t>Mechanic.FacingEDirezionalita</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RT-FEAT-FACTION-SCENARIOS</t>
+          <t>RT-FEAT-MAP-FACING</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>validates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>pianificato</t>
+          <t>wiki:facing-e-direzionalita</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Scenario.Team.Constrine.BastionVektor.OnlyExit</t>
+          <t>Mechanic.FuocoEStati</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RT-FEAT-FACTION-SCENARIOS</t>
+          <t>RT-FEAT-ENV-FIRE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>validates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>pianificato</t>
+          <t>wiki:fuoco-e-stati</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Scenario.Team.Resonance.AuroraKwang.FrozenAnchor</t>
+          <t>Mechanic.FuocoEStati</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RT-FEAT-FACTION-SCENARIOS</t>
+          <t>RT-FEAT-ENV-STATUS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>validates</t>
+          <t>documents</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>pianificato</t>
+          <t>wiki:fuoco-e-stati</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Mechanic.GrigliaEGeometria</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-STANDABILITY</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>wiki:griglia-e-geometria</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Mechanic.GrigliaEGeometria</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-TRANSITION-CLEARANCE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>wiki:griglia-e-geometria</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mechanic.ObiettiviDinamici</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>RT-FEAT-OBJECTIVE-SYSTEM</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>wiki:obiettivi-dinamici</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mechanic.Overwatch</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RT-FEAT-REACTION-OVERWATCH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>wiki:overwatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mechanic.Ponti</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>wiki:ponti</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Mechanic.Porte</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>wiki:porte</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mechanic.TopologiaDinamica</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-INTERACTIVE-EDGES</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>wiki:topologia-dinamica</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mechanic.TopologiaDinamica</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RT-FEAT-MAP-SPECIAL-TRANSITIONS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>wiki:topologia-dinamica</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Scenario.Team.Conflux.FluxRiva.ConductiveFlood</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RT-FEAT-FACTION-SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>validates</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>pianificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Scenario.Team.Constrine.BastionVektor.OnlyExit</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RT-FEAT-FACTION-SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>validates</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>pianificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Scenario.Team.Resonance.AuroraKwang.FrozenAnchor</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RT-FEAT-FACTION-SCENARIOS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>validates</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>pianificato</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Scenario.Team.Sentinel.SteelMurdock.HoldTheLine</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>RT-FEAT-FACTION-SCENARIOS</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>validates</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>pianificato</t>
         </is>
